--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.37702718217334</v>
+        <v>8.348766917103168</v>
       </c>
       <c r="D2" t="n">
-        <v>22.04412872197745</v>
+        <v>3.582170917321335</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1607338711977349</v>
+        <v>0.02611925406963245</v>
       </c>
       <c r="F2" t="n">
-        <v>9.232127669516258</v>
+        <v>1.500220746296392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.69849492456881</v>
+        <v>8.401005425242433</v>
       </c>
       <c r="D3" t="n">
-        <v>40.50838406100996</v>
+        <v>6.582612409914119</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1607338711977349</v>
+        <v>0.02611925406963245</v>
       </c>
       <c r="F3" t="n">
-        <v>9.232127669516258</v>
+        <v>1.500220746296392</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
